--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2022_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2022_los_rios.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 20:20</t>
+    <t xml:space="preserve">2026-08-02 19:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2022_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2022_los_rios.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:59</t>
+    <t xml:space="preserve">2026-08-05 10:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2022_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2022_los_rios.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:55</t>
+    <t xml:space="preserve">2026-08-16 10:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2022_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2022_los_rios.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 10:03</t>
+    <t xml:space="preserve">2026-08-19 13:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2022_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2022_los_rios.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:25</t>
+    <t xml:space="preserve">2026-08-28 12:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2022_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2022_los_rios.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 12:11</t>
+    <t xml:space="preserve">2026-09-06 17:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
